--- a/data/templates/template_month_standard.xlsx
+++ b/data/templates/template_month_standard.xlsx
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E1" s="133" t="inlineStr">
         <is>
-          <t>ימי עבודה בחודש זה (לא כולל שבתות )</t>
+          <t>ימי עבודה בחודש זה (לא כולל {{rest_days}} )</t>
         </is>
       </c>
       <c r="F1" s="133" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="G1" s="133" t="inlineStr">
         <is>
-          <t>שבתות שעבדה בחודש זה</t>
+          <t>{{rest_days}} שעבדה בחודש זה</t>
         </is>
       </c>
       <c r="H1" s="134" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>תשלום בגין עבודה ביום חג או שבת בש"ח</t>
+          <t>תשלום בגין עבודה ביום חג או {{rest_day}} בש"ח</t>
         </is>
       </c>
       <c r="G5" s="50" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>תוספת שבועית בגין ימי שישי - בהתאם לכמות ימי השישי שעבדה באותו חודש</t>
+          <t>תוספת שבועית בגין {{rest_eve_days}} - בהתאם לכמות {{rest_eve_days_definite}} שעבדה באותו חודש</t>
         </is>
       </c>
       <c r="C7" s="124" t="n"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>עבודה בשבת (בהתאם לכמות השבתות שעבדה באותו חודש)</t>
+          <t>עבודה ב{{rest_day}} (בהתאם לכמות {{rest_days_definite}} שעבדה באותו חודש)</t>
         </is>
       </c>
       <c r="C9" s="124" t="n"/>
@@ -2252,7 +2252,7 @@
       <c r="A24" s="24" t="n"/>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>ב. סה"כ  תשלום  עבור  שבתות וחגים</t>
+          <t>ב. סה"כ  תשלום  עבור  {{rest_days}} וחגים</t>
         </is>
       </c>
       <c r="C24" s="22" t="n"/>
@@ -2283,7 +2283,7 @@
     <row r="26" ht="35.25" customHeight="1" thickBot="1">
       <c r="A26" s="188" t="inlineStr">
         <is>
-          <t>ד=א+ב+ג - סה"כ  משכורת בסיסית + תוספת ימי שישי + דמי מחלה+ תשלום עבור שבתות וחגים + ימי חופשה שנוצלו + דמי הבראה +שעות עבודה נוספות בגין אישפוז</t>
+          <t>ד=א+ב+ג - סה"כ  משכורת בסיסית + תוספת {{rest_eve_days}} + דמי מחלה+ תשלום עבור {{rest_days}} וחגים + ימי חופשה שנוצלו + דמי הבראה +שעות עבודה נוספות בגין אישפוז</t>
         </is>
       </c>
       <c r="B26" s="140" t="n"/>
@@ -2357,14 +2357,14 @@
     <row r="33">
       <c r="B33" s="222" t="inlineStr">
         <is>
-          <t>ימי עבודה - תקן (ללא שבתות)</t>
+          <t>ימי עבודה - תקן (ללא {{rest_days}})</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="222" t="inlineStr">
         <is>
-          <t>ימי עבודה בפועל (ללא שבתות)</t>
+          <t>ימי עבודה בפועל (ללא {{rest_days}})</t>
         </is>
       </c>
     </row>

--- a/data/templates/template_month_standard.xlsx
+++ b/data/templates/template_month_standard.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ביטוח רפואי ל{{worker_role}} - שולם באמצעות סוכנות ביטוח הילית בחברת הראל  - קופ"ח  כללית </t>
+          <t xml:space="preserve">ביטוח רפואי ל{{worker_role}} - שולם באמצעות {{insurer}}</t>
         </is>
       </c>
       <c r="C10" s="110" t="n"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B21" s="152" t="inlineStr">
         <is>
-          <t xml:space="preserve">ביטוח לאומי. - הפרשות בגין חודשים               - התשלום  בוצע  ב  </t>
+          <t xml:space="preserve">ביטוח לאומי. - הפרשות בגין חודשים {{ni_months}} - התשלום  בוצע  ב {{ni_paid_on}}</t>
         </is>
       </c>
       <c r="C21" s="137" t="n"/>

--- a/data/templates/template_month_standard.xlsx
+++ b/data/templates/template_month_standard.xlsx
@@ -1794,12 +1794,12 @@
       </c>
       <c r="F1" s="133" t="inlineStr">
         <is>
-          <t>ימי שישי שעבדה בחודש זה</t>
+          <t>ימי שישי {{worked}} בחודש זה</t>
         </is>
       </c>
       <c r="G1" s="133" t="inlineStr">
         <is>
-          <t>{{rest_days}} שעבדה בחודש זה</t>
+          <t>{{rest_days}} {{worked}} בחודש זה</t>
         </is>
       </c>
       <c r="H1" s="134" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I1" s="138" t="inlineStr">
         <is>
-          <t>טור זה  (טור  I )   משמש  טור  עזר למכין  המשכורת  בלבד. יש להסתירו  לפני  הדפסת  תלוש  המשכורת.  יש להחתים  את  העובדת  על  התלוש  ולשלוח  אליה  העתק.</t>
+          <t>טור זה  (טור  I )   משמש  טור  עזר למכין  המשכורת  בלבד. יש להסתירו  לפני  הדפסת  תלוש  המשכורת.  יש להחתים  את  {{worker_definite}}  על  התלוש  ולשלוח  {{to_worker}}  העתק.</t>
         </is>
       </c>
       <c r="J1" s="134" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>תוספת שבועית בגין {{rest_eve_days}} - בהתאם לכמות {{rest_eve_days_definite}} שעבדה באותו חודש</t>
+          <t>תוספת שבועית בגין {{rest_eve_days}} - בהתאם לכמות {{rest_eve_days_definite}} {{worked}} באותו חודש</t>
         </is>
       </c>
       <c r="C7" s="124" t="n"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>עבודה ב{{rest_day}} (בהתאם לכמות {{rest_days_definite}} שעבדה באותו חודש)</t>
+          <t>עבודה ב{{rest_day}} (בהתאם לכמות {{rest_days_definite}} {{worked}} באותו חודש)</t>
         </is>
       </c>
       <c r="C9" s="124" t="n"/>
